--- a/Programming Lab/كشف الوحدة المتدربة.xlsx
+++ b/Programming Lab/كشف الوحدة المتدربة.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C2757-90E7-4AB7-9C54-6A6DFC284BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="3120" yWindow="915" windowWidth="17895" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="قائمة التقييم" sheetId="2" r:id="rId1"/>
@@ -22,6 +23,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -536,22 +540,22 @@
     <t>حمدان خالد حمدان السويدي</t>
   </si>
   <si>
-    <t>مجموعة لواء</t>
-  </si>
-  <si>
-    <t>كتيبة مشاة آلية</t>
-  </si>
-  <si>
-    <t>كتيبة دبابات</t>
-  </si>
-  <si>
-    <t>كتيبة المدفعية</t>
+    <t>قيادة مجموعة اللواء</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة المشاة الآلية/2</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة الدبابات/4</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة المدفعية</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-10C0000]d\ mmmm\ yyyy;@"/>
   </numFmts>
@@ -1066,7 +1070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1200,7 +1204,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:I338"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2908,7 +2912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
